--- a/data/trans_orig/IMC_Medido-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Estudios-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores medido</t>
+          <t>Índice de masa corporal (IMC) medio de los menores medido (tasa de respuesta: 78,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,99; 20,7</t>
+          <t>18,93; 20,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,24; 21,93</t>
+          <t>19,24; 21,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,12; 21,74</t>
+          <t>19,12; 21,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,06; 20,45</t>
+          <t>19,07; 20,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,52; 20,27</t>
+          <t>18,48; 20,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,41; 21,81</t>
+          <t>18,37; 21,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,26; 20,4</t>
+          <t>19,25; 20,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,03; 20,51</t>
+          <t>19,06; 20,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,13; 21,25</t>
+          <t>19,09; 21,28</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,24; 20,0</t>
+          <t>19,23; 19,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,35; 19,0</t>
+          <t>18,39; 19,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,88; 21,32</t>
+          <t>18,92; 21,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,61; 20,41</t>
+          <t>19,59; 20,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,6; 19,27</t>
+          <t>18,61; 19,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,36; 20,48</t>
+          <t>19,36; 20,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,56; 20,1</t>
+          <t>19,55; 20,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,61; 19,07</t>
+          <t>18,61; 19,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,36; 20,69</t>
+          <t>19,35; 20,62</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,32; 20,23</t>
+          <t>18,34; 20,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,97; 19,29</t>
+          <t>17,99; 19,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,53; 19,29</t>
+          <t>17,33; 19,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,64; 19,79</t>
+          <t>18,63; 19,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,3; 19,74</t>
+          <t>18,26; 19,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,64; 19,24</t>
+          <t>17,65; 19,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,66; 19,73</t>
+          <t>18,63; 19,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,28; 19,2</t>
+          <t>18,3; 19,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,71; 18,86</t>
+          <t>17,73; 18,87</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,19; 19,89</t>
+          <t>19,18; 19,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,52; 19,07</t>
+          <t>18,5; 19,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,79; 20,65</t>
+          <t>18,81; 20,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,48; 20,08</t>
+          <t>19,49; 20,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,31</t>
+          <t>18,72; 19,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,06; 19,96</t>
+          <t>19,09; 19,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,43; 19,87</t>
+          <t>19,43; 19,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,08</t>
+          <t>18,68; 19,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,11; 20,13</t>
+          <t>19,09; 20,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_Medido-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Estudios-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores medido (tasa de respuesta: 78,69%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 78,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,93; 20,63</t>
+          <t>18,97; 20,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,24; 21,9</t>
+          <t>19,21; 21,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,12; 21,96</t>
+          <t>19,17; 21,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,07; 20,52</t>
+          <t>19,05; 20,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,48; 20,41</t>
+          <t>18,51; 20,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,37; 21,66</t>
+          <t>18,3; 21,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,25; 20,37</t>
+          <t>19,26; 20,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,06; 20,63</t>
+          <t>19,03; 20,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,09; 21,28</t>
+          <t>19,13; 21,46</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,23; 19,96</t>
+          <t>19,28; 20,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,39; 19,02</t>
+          <t>18,41; 19,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,92; 21,17</t>
+          <t>18,93; 21,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,59; 20,42</t>
+          <t>19,61; 20,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,61; 19,31</t>
+          <t>18,62; 19,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,36; 20,45</t>
+          <t>19,33; 20,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,55; 20,09</t>
+          <t>19,54; 20,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,61; 19,06</t>
+          <t>18,6; 19,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,35; 20,62</t>
+          <t>19,36; 20,69</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,34; 20,17</t>
+          <t>18,38; 20,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,99; 19,27</t>
+          <t>18,0; 19,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,33; 19,07</t>
+          <t>17,45; 19,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,63; 19,87</t>
+          <t>18,65; 19,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,26; 19,65</t>
+          <t>18,34; 19,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,65; 19,32</t>
+          <t>17,67; 19,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,63; 19,73</t>
+          <t>18,62; 19,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,3; 19,21</t>
+          <t>18,33; 19,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,73; 18,87</t>
+          <t>17,71; 18,86</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,18; 19,83</t>
+          <t>19,17; 19,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,5; 19,04</t>
+          <t>18,5; 19,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,81; 20,72</t>
+          <t>18,78; 20,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,49; 20,09</t>
+          <t>19,47; 20,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,72; 19,26</t>
+          <t>18,7; 19,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,09; 19,96</t>
+          <t>19,07; 20,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,43; 19,88</t>
+          <t>19,45; 19,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,09</t>
+          <t>18,68; 19,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,09; 20,14</t>
+          <t>19,12; 20,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_Medido-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Estudios-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19,76</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19,36</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20,27</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>19,78</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>20,11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20,32</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19,76</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19,36</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,81</t>
+          <t>20,27</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20,05</t>
+          <t>20,27</t>
         </is>
       </c>
     </row>
@@ -677,32 +677,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,97; 20,77</t>
+          <t>19,06; 20,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,21; 21,78</t>
+          <t>18,52; 20,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,17; 21,87</t>
+          <t>18,87; 22,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,05; 20,48</t>
+          <t>18,99; 20,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,51; 20,33</t>
+          <t>19,24; 21,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,3; 21,7</t>
+          <t>19,15; 21,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,13; 21,46</t>
+          <t>19,39; 21,5</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19,99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18,96</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19,98</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>19,62</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>18,68</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>19,84</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,99</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>18,96</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,89</t>
+          <t>19,18</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19,87</t>
+          <t>19,63</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,28; 20,02</t>
+          <t>19,61; 20,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,41; 19,02</t>
+          <t>18,6; 19,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,93; 21,36</t>
+          <t>19,46; 20,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,61; 20,41</t>
+          <t>19,24; 20,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,62; 19,35</t>
+          <t>18,35; 19,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,33; 20,49</t>
+          <t>18,65; 20,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,54; 20,09</t>
+          <t>19,56; 20,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,6; 19,06</t>
+          <t>18,61; 19,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,36; 20,69</t>
+          <t>19,23; 20,06</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19,17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18,86</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18,35</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>19,01</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>18,52</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18,23</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,17</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,86</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,24</t>
+          <t>18,34</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18,24</t>
+          <t>18,34</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,38; 20,37</t>
+          <t>18,64; 19,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,0; 19,3</t>
+          <t>18,3; 19,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,45; 19,19</t>
+          <t>17,72; 19,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,65; 19,86</t>
+          <t>18,32; 20,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,34; 19,74</t>
+          <t>17,97; 19,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,67; 19,32</t>
+          <t>17,66; 19,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,62; 19,71</t>
+          <t>18,66; 19,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,33; 19,22</t>
+          <t>18,28; 19,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,71; 18,86</t>
+          <t>17,79; 18,99</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19,78</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18,98</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19,61</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>19,5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>18,77</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19,48</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19,78</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,98</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,49</t>
+          <t>19,03</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19,48</t>
+          <t>19,35</t>
         </is>
       </c>
     </row>
@@ -1007,37 +1007,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,17; 19,86</t>
+          <t>19,48; 20,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,5; 19,06</t>
+          <t>18,68; 19,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,78; 20,68</t>
+          <t>19,19; 20,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,47; 20,08</t>
+          <t>19,19; 19,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,7; 19,31</t>
+          <t>18,52; 19,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,07; 20,01</t>
+          <t>18,59; 19,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,45; 19,89</t>
+          <t>19,43; 19,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,12; 20,15</t>
+          <t>19,03; 19,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_Medido-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 78,69%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 81,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>19,76</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>19,36</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20,27</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19,78</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20,11</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,27</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,77</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19,69</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20,27</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>19.76359495516591</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>19.35516883264248</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>20.26977106692162</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>19.7806772906788</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>20.11121772875125</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>20.27034186265277</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>19.77239824237896</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>19.6876618062628</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>20.2700222714629</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>19,06; 20,45</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>18,52; 20,27</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18,87; 22,22</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18,99; 20,7</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>19,24; 21,93</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>19,15; 21,53</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>19,26; 20,4</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19,03; 20,51</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19,39; 21,5</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>19.05799704796775</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>18.51771512155855</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>18.87365806792391</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>18.99363953328083</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>19.23527740985971</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>19.15045210310036</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>19.26484477350148</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>19.03156196307469</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>19.39496611187804</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>20.4478436003803</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>20.27309674348498</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>22.221947338971</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>20.69881096372023</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>21.92972210439239</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>21.52537785464481</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>20.40384329965547</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>20.51489544275627</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>21.50071934687038</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>19,99</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>18,96</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>19,98</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,62</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>18,68</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>19,18</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,82</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18,83</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19,63</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>19,61; 20,41</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>18,6; 19,27</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>19,46; 20,57</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19,24; 20,0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>18,35; 19,0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,65; 20,02</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,56; 20,1</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18,61; 19,07</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>19,23; 20,06</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>19.99299536246416</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>18.95955733718818</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>19.97863505019741</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>19.62316313014414</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>18.68407066178947</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>19.1755679853059</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>19.81615142969532</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>18.82683603704094</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>19.63236471787008</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>19,17</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>18,86</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18,35</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,01</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,52</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,34</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19,09</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18,7</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>18,34</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>19.60515156016809</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>18.60192964048418</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>19.46079779319103</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>19.24164361142892</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>18.35289720952992</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>18.64865187335479</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>19.5631819251287</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>18.60637822624397</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>19.22690582912014</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>18,64; 19,79</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>18,3; 19,74</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>17,72; 19,44</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>18,32; 20,23</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>17,97; 19,29</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>17,66; 19,49</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>18,66; 19,73</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>18,28; 19,2</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>17,79; 18,99</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>20.41209199139702</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>19.27131441568183</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>20.56551368050033</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>20.00205114797622</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>18.99749638045857</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>20.02451928414626</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>20.10230353505012</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>19.06879953521748</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>20.05904466924744</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,107 +845,215 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>19,78</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18,98</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19,61</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19,5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,77</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,03</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,65</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18,88</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>19,35</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>19.17039289897436</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>18.86155084569194</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>18.34522872876893</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>19.00600990972685</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>18.51688002321614</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>18.3437665830732</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>19.08803588837503</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>18.69556498125223</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>18.34452612643492</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>19,48; 20,08</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>18,68; 19,31</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>19,19; 20,09</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19,19; 19,89</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>18,52; 19,07</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18,59; 19,64</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>19,43; 19,87</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>18,68; 19,08</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>19,03; 19,72</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>18.64185069602872</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>18.30207473627849</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>17.72365628564516</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>18.32321244119274</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>17.97034397172942</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>17.66082143927071</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>18.65611080273137</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>18.2751573618936</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>17.79441224003918</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>19.78632612955307</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>19.73587740412842</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>19.44210152194172</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>20.22886268693641</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>19.28714140203391</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>19.49316337782738</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>19.73289330536301</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>19.19844079128241</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>18.98526893324451</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>19.7832102567173</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>18.97777263197639</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>19.60638206017093</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>19.50069028820386</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>18.77159943671817</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>19.02804702611655</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>19.64530849799545</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>18.87929111441086</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>19.34922524819753</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>19.48408026658085</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>18.68351430363325</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>19.18738829380854</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>19.18925687107792</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>18.52246053296223</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>18.5874032879561</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>19.4301255017699</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>18.67598961102727</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>19.02584372129917</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>20.08231176837277</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>19.31294092105166</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>20.08517271000238</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>19.88627677988524</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>19.06876213998896</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>19.63538699048732</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>19.86657712752194</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>19.07831773694881</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>19.72405907292973</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1061,13 +1062,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/IMC_Medido-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Estudios-trans_orig.xlsx
@@ -528,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 81,88%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 78,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
